--- a/astro-site/public/dl/pizza-shop-checklist-templates/05-pizzeria-cleaning-checklist-inventory-maintenance.xlsx
+++ b/astro-site/public/dl/pizza-shop-checklist-templates/05-pizzeria-cleaning-checklist-inventory-maintenance.xlsx
@@ -733,10 +733,10 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
+    <row r="8" ht="47" customHeight="1">
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>▸ The monthly tab keeps the checks your own team does (hood filters, a look at the extinguisher): they don't replace the contracted inspection, they prepare for it.</t>
+          <t>▸ The monthly tab mixes your team's own checks (hood filters, a look at the extinguisher, first-aid kit) with the monthly ones for a technician or qualified person (oven, wood-fired exhaust, gas valves): they don't replace the contracted services in "Quarterly &amp; Annual", they prepare for them.</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>00 flour</t>
+          <t>00 or high-gluten flour</t>
         </is>
       </c>
       <c r="B7" s="12" t="n"/>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7" s="14">
         <f>IF(B7="","",IF(B7&lt;D7,"⚠️ REORDER","OK"))</f>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" s="10">
         <f>IF(B8="","",IF(B8&lt;D8,"⚠️ REORDER","OK"))</f>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="10">
         <f>IF(B10="","",IF(B10&lt;D10,"⚠️ REORDER","OK"))</f>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" s="10">
         <f>IF(B12="","",IF(B12&lt;D12,"⚠️ REORDER","OK"))</f>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E20" s="10">
         <f>IF(B20="","",IF(B20&lt;D20,"⚠️ REORDER","OK"))</f>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="10">
         <f>IF(B22="","",IF(B22&lt;D22,"⚠️ REORDER","OK"))</f>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" s="10">
         <f>IF(B24="","",IF(B24&lt;D24,"⚠️ REORDER","OK"))</f>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" s="14">
         <f>IF(B27="","",IF(B27&lt;D27,"⚠️ REORDER","OK"))</f>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34" s="10">
         <f>IF(B34="","",IF(B34&lt;D34,"⚠️ REORDER","OK"))</f>
@@ -1661,7 +1661,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Delivery bags</t>
+          <t>To-go bags (paper / plastic)</t>
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Pizza maker</t>
         </is>
       </c>
       <c r="E8" s="29" t="inlineStr">
@@ -3208,9 +3208,9 @@
       <c r="A11" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>Dish machine: filters, rinse aid, softener salt</t>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>Dish machine: filters, rinse aid and chemical levels (water softener salt only if you have a softener)</t>
         </is>
       </c>
       <c r="C11" s="29" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="B12" s="38" t="inlineStr">
         <is>
-          <t>Exhaust hood: degrease and replace filters; the contractor cleans the DUCTS (see "Quarterly &amp; Annual")</t>
+          <t>Exhaust hood: degrease the hood and check the filters (replace only bent or damaged ones); the contractor cleans the DUCTS (see "Quarterly &amp; Annual")</t>
         </is>
       </c>
       <c r="C12" s="29" t="inlineStr">
